--- a/topic_3_img/Topic 3 Sol.xlsx
+++ b/topic_3_img/Topic 3 Sol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Github/lecture_financial_statements_analysis/topic_3_img/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B145DBC-D109-1745-9F16-7DAF5F90DEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AD8BA5-B3D2-E244-9E6F-6BD0E7625ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1980" windowWidth="40960" windowHeight="20840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4900" yWindow="600" windowWidth="36060" windowHeight="20640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_receivables" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="59">
   <si>
     <t>Accounting events: sale and allowance for bad debt</t>
   </si>
@@ -239,10 +239,13 @@
     <t>Cash Flows Statement (year t+1)</t>
   </si>
   <si>
-    <t>notice the sign!!!!</t>
-  </si>
-  <si>
     <t>How can the estimation of doubtfull accounts be used to move profits/losses across years?</t>
+  </si>
+  <si>
+    <t>only $800 of Receivables was actually converted into cash!</t>
+  </si>
+  <si>
+    <t>note the sign!!!!</t>
   </si>
 </sst>
 </file>
@@ -297,17 +300,17 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="8"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -405,14 +408,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -453,11 +450,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -481,15 +490,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>326160</xdr:colOff>
+      <xdr:colOff>731314</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>60480</xdr:rowOff>
+      <xdr:rowOff>83854</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1347120</xdr:colOff>
+      <xdr:colOff>1752274</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:rowOff>91774</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -504,8 +513,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="326160" y="60480"/>
-          <a:ext cx="3459240" cy="1145880"/>
+          <a:off x="731314" y="83854"/>
+          <a:ext cx="3638874" cy="1153257"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -584,25 +593,6 @@
               <a:latin typeface="Times New Roman"/>
             </a:rPr>
             <a:t>1) What is the impact on the financial statements of the sale and collection risk for this year?</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" b="0" strike="noStrike" spc="-1">
-            <a:latin typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>2) What if the customers just pay $800 of their debt?</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1000" b="0" strike="noStrike" spc="-1">
             <a:latin typeface="Times New Roman"/>
@@ -1523,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B10:M44"/>
+  <dimension ref="B10:M47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="28" customWidth="1"/>
@@ -1533,374 +1523,406 @@
   </cols>
   <sheetData>
     <row r="10" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="I12" s="2" t="s">
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="I12" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="L12" s="2" t="s">
+      <c r="J12" s="27"/>
+      <c r="L12" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="27"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="I13" s="7" t="s">
+      <c r="G13" s="4"/>
+      <c r="I13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="8"/>
-      <c r="L13" s="4" t="s">
+      <c r="J13" s="6"/>
+      <c r="L13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="2"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D15" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E15" s="30">
         <v>1000</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="I14" s="7" t="s">
+      <c r="G15" s="6"/>
+      <c r="I15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J15" s="6">
         <v>1000</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="29" t="s">
+      <c r="L15" s="5"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E16" s="31">
         <v>-50</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="6"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D16" s="28" t="s">
+      <c r="G16" s="4"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="10">
-        <f>E15+E14</f>
+      <c r="E17" s="8">
+        <f>E16+E15</f>
         <v>950</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="I16" s="4" t="s">
+      <c r="G17" s="4"/>
+      <c r="I17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="L16" s="4" t="s">
+      <c r="J17" s="6"/>
+      <c r="L17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D17" s="7"/>
-      <c r="E17" s="9"/>
-      <c r="G17" s="8"/>
-      <c r="I17" s="7" t="s">
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D18" s="5"/>
+      <c r="E18" s="7"/>
+      <c r="G18" s="6"/>
+      <c r="I18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J18" s="6">
         <v>-50</v>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="I18" s="15" t="s">
+      <c r="L18" s="5"/>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="I19" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="16"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="16"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B21" s="3" t="s">
+      <c r="J19" s="14"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="14"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D23" s="2" t="s">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D24" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="I23" s="2" t="s">
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="I24" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="L23" s="2" t="s">
+      <c r="J24" s="27"/>
+      <c r="L24" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D24" s="4" t="s">
+      <c r="M24" s="27"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="I24" s="7" t="s">
+      <c r="G25" s="4"/>
+      <c r="I25" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="8"/>
-      <c r="L24" s="4" t="s">
+      <c r="J25" s="6"/>
+      <c r="L25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D25" s="7" t="s">
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="4"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="6"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E27" s="7">
         <v>800</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
-      <c r="L25" s="7" t="s">
+      <c r="G27" s="6"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="6"/>
+      <c r="L27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M27" s="6">
         <v>800</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D26" s="29" t="s">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D28" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E28" s="30">
         <v>-800</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="8"/>
-    </row>
-    <row r="27" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="29" t="s">
+      <c r="G28" s="4"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="6"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E29" s="31">
         <v>-150</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="I27" s="4" t="s">
+      <c r="G29" s="4"/>
+      <c r="I29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="L27" s="4" t="s">
+      <c r="J29" s="6"/>
+      <c r="L29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D28" s="28" t="s">
+      <c r="M29" s="6"/>
+    </row>
+    <row r="30" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="10">
-        <f>E27+E26</f>
+      <c r="E30" s="8">
+        <f>E29+E28</f>
         <v>-950</v>
       </c>
-      <c r="G28" s="8"/>
-      <c r="I28" s="7" t="s">
+      <c r="G30" s="6"/>
+      <c r="I30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J30" s="6">
         <v>-150</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
-      <c r="I29" s="15" t="s">
+      <c r="L30" s="5"/>
+      <c r="M30" s="6"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D31" s="9"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="I31" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="16"/>
+      <c r="J31" s="14"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="14"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D34" s="2" t="s">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D36" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="I34" s="2" t="s">
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="I36" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="J34" s="2"/>
-      <c r="L34" s="2" t="s">
+      <c r="J36" s="27"/>
+      <c r="L36" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D35" s="4" t="s">
+      <c r="M36" s="27"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="I35" s="7" t="s">
+      <c r="G37" s="4"/>
+      <c r="I37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="8"/>
-      <c r="L35" s="4" t="s">
+      <c r="J37" s="6"/>
+      <c r="L37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D36" s="7" t="s">
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D38" s="2"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="6"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E39" s="7">
         <v>1000</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="8"/>
-      <c r="L36" s="7" t="s">
+      <c r="G39" s="6"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="6"/>
+      <c r="L39" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M36" s="8">
+      <c r="M39" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D37" s="29" t="s">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D40" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E40" s="32">
         <v>-1000</v>
       </c>
-      <c r="G37" s="6"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="29" t="s">
+      <c r="G40" s="4"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="6"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="6"/>
+    </row>
+    <row r="41" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E41" s="33">
         <v>50</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="I38" s="4" t="s">
+      <c r="G41" s="4"/>
+      <c r="I41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J38" s="8"/>
-      <c r="L38" s="4" t="s">
+      <c r="J41" s="6"/>
+      <c r="L41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="8"/>
-    </row>
-    <row r="39" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="D39" s="28" t="s">
+      <c r="M41" s="6"/>
+    </row>
+    <row r="42" spans="2:13" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="D42" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="10">
-        <f>E38+E37</f>
+      <c r="E42" s="8">
+        <f>E41+E40</f>
         <v>-950</v>
       </c>
-      <c r="G39" s="8"/>
-      <c r="I39" s="7" t="s">
+      <c r="G42" s="6"/>
+      <c r="I42" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J42" s="6">
         <v>50</v>
       </c>
-      <c r="K39" s="32" t="s">
+      <c r="K42" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="6"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="12"/>
+      <c r="I43" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="14"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="14"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B47" t="s">
         <v>56</v>
-      </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="8"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D40" s="11"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14"/>
-      <c r="I40" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="16"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="16"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B44" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="L36:M36"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="L12:M12"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="L24:M24"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1917,7 +1939,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="11.5" style="17"/>
+    <col min="1" max="16384" width="11.5" style="15"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -1940,127 +1962,127 @@
   </cols>
   <sheetData>
     <row r="13" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="16">
         <v>15000</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="C15" s="19"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="19">
         <v>15000</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>5000</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <f>C16+C17</f>
         <v>20000</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="C19" s="19"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <f>+C18+C14</f>
         <v>35000</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="17">
         <v>1000</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="19">
         <v>19000</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="19">
         <f>+C20-C22</f>
         <v>16000</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <f>C23+C22</f>
         <v>35000</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="28"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="16">
         <v>2000</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="16">
         <f>C28*0.35</f>
         <v>700</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="16">
         <f>+C28-C29</f>
         <v>1300</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2138,12 +2160,12 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13" t="s">
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="11">
         <v>1000</v>
       </c>
     </row>
@@ -2163,7 +2185,7 @@
       <c r="A52" t="s">
         <v>47</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="23" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2173,22 +2195,22 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="26" t="s">
+      <c r="C56" s="28"/>
+      <c r="D56" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E56" s="26" t="s">
+      <c r="E56" s="24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="18">
+      <c r="C57" s="16">
         <f>+C28</f>
         <v>2000</v>
       </c>
@@ -2196,16 +2218,16 @@
         <f>-E50</f>
         <v>-2600</v>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="16">
         <f>+C57+D57</f>
         <v>-600</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C58" s="18">
+      <c r="C58" s="16">
         <f>+C29</f>
         <v>700</v>
       </c>
@@ -2213,16 +2235,16 @@
         <f>+D57*35%</f>
         <v>-909.99999999999989</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="16">
         <f>E57*0.35</f>
         <v>-210</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="18">
+      <c r="C59" s="16">
         <f>+C30</f>
         <v>1300</v>
       </c>
@@ -2230,129 +2252,129 @@
         <f>+D57-D58</f>
         <v>-1690</v>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="16">
         <f>+E57-E58</f>
         <v>-390</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="28"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="18">
+      <c r="C63" s="16">
         <v>15000</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="17">
         <f>+C63+D63</f>
         <v>15000</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="C64" s="19"/>
-      <c r="E64" s="19"/>
+      <c r="C64" s="17"/>
+      <c r="E64" s="17"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="19">
+      <c r="C65" s="17">
         <v>15000</v>
       </c>
       <c r="D65">
         <f>-E50</f>
         <v>-2600</v>
       </c>
-      <c r="E65" s="19">
+      <c r="E65" s="17">
         <f>+C65+D65</f>
         <v>12400</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="19">
+      <c r="C66" s="17">
         <v>5000</v>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="17">
         <f>+C66+D66</f>
         <v>5000</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="16">
         <f>C65+C66</f>
         <v>20000</v>
       </c>
-      <c r="E67" s="18">
+      <c r="E67" s="16">
         <f>E65+E66</f>
         <v>17400</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="C68" s="19"/>
-      <c r="E68" s="19"/>
+      <c r="C68" s="17"/>
+      <c r="E68" s="17"/>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="22">
         <f>+C67+C63</f>
         <v>35000</v>
       </c>
-      <c r="E69" s="18">
+      <c r="E69" s="16">
         <f>+E67+E63</f>
         <v>32400</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B70" s="3"/>
-      <c r="C70" s="18"/>
-      <c r="E70" s="18"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="16"/>
+      <c r="E70" s="16"/>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="19">
+      <c r="C71" s="17">
         <v>1000</v>
       </c>
       <c r="D71">
         <f>+D58</f>
         <v>-909.99999999999989</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71" s="17">
         <f>+C71+D71</f>
         <v>90.000000000000114</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C72" s="19">
+      <c r="C72" s="17">
         <v>19000</v>
       </c>
-      <c r="E72" s="19">
+      <c r="E72" s="17">
         <f>+C72+D72</f>
         <v>19000</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C73" s="19">
+      <c r="C73" s="17">
         <f>+C69-C72-C71</f>
         <v>15000</v>
       </c>
@@ -2360,20 +2382,20 @@
         <f>+D59</f>
         <v>-1690</v>
       </c>
-      <c r="E73" s="19">
+      <c r="E73" s="17">
         <f>+C73+D73</f>
         <v>13310</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B74" s="23" t="s">
+      <c r="B74" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="24">
+      <c r="C74" s="22">
         <f>C73+C72+C71</f>
         <v>35000</v>
       </c>
-      <c r="E74" s="18">
+      <c r="E74" s="16">
         <f>E73+E72+E71</f>
         <v>32400</v>
       </c>

--- a/topic_3_img/Topic 3 Sol.xlsx
+++ b/topic_3_img/Topic 3 Sol.xlsx
@@ -450,12 +450,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -468,6 +462,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1528,20 +1528,20 @@
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="I12" s="27" t="s">
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="I12" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="27"/>
-      <c r="L12" s="27" t="s">
+      <c r="J12" s="33"/>
+      <c r="L12" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="27"/>
+      <c r="M12" s="33"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D13" s="2" t="s">
@@ -1570,10 +1570,10 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="28">
         <v>1000</v>
       </c>
       <c r="G15" s="6"/>
@@ -1587,10 +1587,10 @@
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="29">
         <v>-50</v>
       </c>
       <c r="G16" s="4"/>
@@ -1651,20 +1651,20 @@
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="I24" s="27" t="s">
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="I24" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="J24" s="27"/>
-      <c r="L24" s="27" t="s">
+      <c r="J24" s="33"/>
+      <c r="L24" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="M24" s="27"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D25" s="2" t="s">
@@ -1710,10 +1710,10 @@
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="28">
         <v>-800</v>
       </c>
       <c r="G28" s="4"/>
@@ -1723,10 +1723,10 @@
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="29">
         <v>-150</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1773,7 +1773,7 @@
       <c r="M31" s="14"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="32" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1783,20 +1783,20 @@
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="I36" s="27" t="s">
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="I36" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="27"/>
-      <c r="L36" s="27" t="s">
+      <c r="J36" s="33"/>
+      <c r="L36" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="27"/>
+      <c r="M36" s="33"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D37" s="2" t="s">
@@ -1842,10 +1842,10 @@
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="30">
         <v>-1000</v>
       </c>
       <c r="G40" s="4"/>
@@ -1855,10 +1855,10 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="2:13" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="31">
         <v>50</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1889,7 +1889,7 @@
       <c r="J42" s="6">
         <v>50</v>
       </c>
-      <c r="K42" s="34" t="s">
+      <c r="K42" s="32" t="s">
         <v>58</v>
       </c>
       <c r="L42" s="5"/>
@@ -1962,10 +1962,10 @@
   </cols>
   <sheetData>
     <row r="13" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B14" s="1" t="s">
@@ -2050,10 +2050,10 @@
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="28"/>
+      <c r="C27" s="34"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B28" s="1" t="s">
@@ -2195,10 +2195,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="28"/>
+      <c r="C56" s="34"/>
       <c r="D56" s="24" t="s">
         <v>50</v>
       </c>
@@ -2258,10 +2258,10 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="28"/>
+      <c r="C61" s="34"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B63" s="1" t="s">
